--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/MAINE_2014.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/MAINE_2014.xlsx
@@ -463,7 +463,7 @@
         <v>2</v>
       </c>
       <c r="D6">
-        <v>0.095238095238095</v>
+        <v>0.09523809523809501</v>
       </c>
     </row>
     <row r="7">
@@ -481,7 +481,7 @@
         <v>2</v>
       </c>
       <c r="D7">
-        <v>0.095238095238095</v>
+        <v>0.09523809523809501</v>
       </c>
     </row>
     <row r="8">
